--- a/data/proteomics/volume_size_across_go_term_Rosemary.xlsx
+++ b/data/proteomics/volume_size_across_go_term_Rosemary.xlsx
@@ -4823,58 +4823,58 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.01142167930631724</v>
+        <v>0.009877696763667931</v>
       </c>
       <c r="D69" t="n">
-        <v>0.01013401106927783</v>
+        <v>0.008832269635326028</v>
       </c>
       <c r="E69" t="n">
-        <v>0.01124096792115624</v>
+        <v>0.009540671053870855</v>
       </c>
       <c r="F69" t="n">
-        <v>0.009653095616876786</v>
+        <v>0.008231863672745945</v>
       </c>
       <c r="G69" t="n">
-        <v>0.01019669818618219</v>
+        <v>0.008770668751616334</v>
       </c>
       <c r="H69" t="n">
-        <v>0.01486277689268383</v>
+        <v>0.01244029451654075</v>
       </c>
       <c r="I69" t="n">
-        <v>0.01599058680332789</v>
+        <v>0.01377201680814652</v>
       </c>
       <c r="J69" t="n">
-        <v>0.01398291337260849</v>
+        <v>0.01193453970121495</v>
       </c>
       <c r="K69" t="n">
-        <v>0.01391665068461304</v>
+        <v>0.0119667467523891</v>
       </c>
       <c r="L69" t="n">
-        <v>0.01649627748327403</v>
+        <v>0.01429230713193208</v>
       </c>
       <c r="M69" t="n">
-        <v>0.01669995161618129</v>
+        <v>0.01421681168968719</v>
       </c>
       <c r="N69" t="n">
-        <v>0.016278011279327</v>
+        <v>0.01398295579545476</v>
       </c>
       <c r="O69" t="n">
-        <v>0.03198940565031302</v>
+        <v>0.02764256200191795</v>
       </c>
       <c r="P69" t="n">
-        <v>0.03251584384923078</v>
+        <v>0.0278894422873185</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.02997990270099748</v>
+        <v>0.02530813906401628</v>
       </c>
       <c r="R69" t="n">
-        <v>0.04401428079516585</v>
+        <v>0.03753668368379381</v>
       </c>
       <c r="S69" t="n">
-        <v>0.04697544936073398</v>
+        <v>0.04027840178211868</v>
       </c>
       <c r="T69" t="n">
-        <v>0.04442009054254545</v>
+        <v>0.03820305915643188</v>
       </c>
     </row>
     <row r="70">
